--- a/data/batches/B03_SpecialPurpose_SE_SM_SV_DI/Test_Validation_Report/Test_Validation_Report_B03.xlsx
+++ b/data/batches/B03_SpecialPurpose_SE_SM_SV_DI/Test_Validation_Report/Test_Validation_Report_B03.xlsx
@@ -9732,11 +9732,7 @@
           <t>INCONSISTENT_CD</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>INCONSISTENT_CD</t>
-        </is>
-      </c>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -9744,22 +9740,22 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Duplicate with mutation verified successfully</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
